--- a/final_outputs/final_tables_formatted.xlsx
+++ b/final_outputs/final_tables_formatted.xlsx
@@ -493,7 +493,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-13.2684</v>
+        <v>-13.5226</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-58.1759</v>
+        <v>-212.0164</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-14.498</v>
+        <v>-14.7088</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-66.3631</v>
+        <v>-67.1942</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-59.8097</v>
+        <v>-60.8838</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-59.8844</v>
+        <v>-60.9814</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-10.5423</v>
+        <v>-11.1466</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-57.1782</v>
+        <v>-57.9748</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-58.1564</v>
+        <v>-25.3159</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-58.1817</v>
+        <v>-59.5131</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-11.1314</v>
+        <v>-11.2273</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-61.6132</v>
+        <v>-62.3257</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -763,27 +763,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000005, 0.000034]</t>
+          <t>[-0.000037, 0.000036]</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>-0.000003</t>
+          <t>-0.000006</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000017, 0.000013]</t>
+          <t>[-0.000021, 0.000008]</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>-0.000015</t>
+          <t>-0.000018</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000038, 0.000017]</t>
+          <t>[-0.000046, 0.000011]</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>0.000031</t>
+          <t>0.000014</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000004, 0.000078]</t>
+          <t>[-0.000068, 0.000060]</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0.000007</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000028, 0.000034]</t>
+          <t>[-0.000039, 0.000029]</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>0.000019</t>
+          <t>0.000009</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000040, 0.000068]</t>
+          <t>[-0.000055, 0.000068]</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>0.000029</t>
+          <t>-0.000016</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000030, 0.000110]</t>
+          <t>[-0.000107, 0.000088]</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.000017</t>
+          <t>0.000006</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000057]</t>
+          <t>[-0.000042, 0.000051]</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>0.000027</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000036, 0.000089]</t>
+          <t>[-0.000060, 0.000098]</t>
         </is>
       </c>
     </row>
@@ -878,32 +878,32 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>0.000017</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[-0.000070, 0.000095]</t>
+          <t>[-0.000104, 0.000071]</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.000038</t>
+          <t>0.000031</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[-0.000013, 0.000092]</t>
+          <t>[-0.000041, 0.000084]</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-0.000000</t>
+          <t>-0.000026</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[-0.000060, 0.000110]</t>
+          <t>[-0.000115, 0.000080]</t>
         </is>
       </c>
     </row>
@@ -918,32 +918,32 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>0.000002</t>
+          <t>-0.000009</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000022, 0.000027]</t>
+          <t>[-0.000039, 0.000020]</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000003</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000005, 0.000018]</t>
+          <t>[-0.000011, 0.000016]</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0.000001</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000019, 0.000020]</t>
+          <t>[-0.000031, 0.000017]</t>
         </is>
       </c>
     </row>
@@ -958,32 +958,32 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>-0.000016</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>[-0.000032, 0.000058]</t>
+          <t>[-0.000076, 0.000046]</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0.000019</t>
+          <t>0.000009</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>[-0.000009, 0.000051]</t>
+          <t>[-0.000019, 0.000045]</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-0.000010</t>
+          <t>-0.000027</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>[-0.000056, 0.000054]</t>
+          <t>[-0.000077, 0.000048]</t>
         </is>
       </c>
     </row>
@@ -998,32 +998,32 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>-0.000015</t>
+          <t>-0.000063</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>[-0.000088, 0.000049]</t>
+          <t>[-0.000140, 0.000029]</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>-0.000004</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>[-0.000037, 0.000045]</t>
+          <t>[-0.000047, 0.000035]</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-0.000018</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>[-0.000074, 0.000044]</t>
+          <t>[-0.000087, 0.000033]</t>
         </is>
       </c>
     </row>
@@ -1038,32 +1038,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>-0.000013</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>[-0.000086, 0.000056]</t>
+          <t>[-0.000098, 0.000061]</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-0.000045</t>
+          <t>-0.000064</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>[-0.000097, 0.000005]</t>
+          <t>[-0.000108, 0.000002]</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-0.000011</t>
+          <t>-0.000021</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>[-0.000094, 0.000050]</t>
+          <t>[-0.000112, 0.000048]</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000020</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>[-0.000033, 0.000004]</t>
+          <t>[-0.000063, 0.000005]</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1093,17 +1093,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>[-0.000016, 0.000006]</t>
+          <t>[-0.000017, 0.000006]</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-0.000028</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>[-0.000051, 0.000009]</t>
+          <t>[-0.000062, 0.000006]</t>
         </is>
       </c>
     </row>
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>-0.000010</t>
+          <t>-0.000038</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>[-0.000046, 0.000039]</t>
+          <t>[-0.000127, 0.000040]</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-0.000003</t>
+          <t>-0.000014</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>[-0.000025, 0.000015]</t>
+          <t>[-0.000039, 0.000011]</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>0.000001</t>
+          <t>-0.000040</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>[-0.000068, 0.000036]</t>
+          <t>[-0.000107, 0.000024]</t>
         </is>
       </c>
     </row>
@@ -1158,32 +1158,32 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000036</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>[-0.000051, 0.000069]</t>
+          <t>[-0.000183, 0.000036]</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0.000007</t>
+          <t>-0.000011</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000060]</t>
+          <t>[-0.000058, 0.000051]</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-0.000003</t>
+          <t>-0.000036</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>[-0.000071, 0.000070]</t>
+          <t>[-0.000149, 0.000038]</t>
         </is>
       </c>
     </row>
@@ -1198,32 +1198,32 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>0.000029</t>
+          <t>-0.000005</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>[-0.000045, 0.000095]</t>
+          <t>[-0.000187, 0.000068]</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0.000027</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>[-0.000023, 0.000076]</t>
+          <t>[-0.000054, 0.000065]</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-0.000033</t>
+          <t>-0.000038</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>[-0.000127, 0.000019]</t>
+          <t>[-0.000151, 0.000001]</t>
         </is>
       </c>
     </row>
@@ -1238,32 +1238,32 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0.000016</t>
+          <t>0.000003</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>[-0.000008, 0.000031]</t>
+          <t>[-0.000068, 0.000026]</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>-0.000010</t>
+          <t>-0.000016</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>[-0.000024, 0.000009]</t>
+          <t>[-0.000031, 0.000004]</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-0.000025*</t>
+          <t>-0.000032*</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>[-0.000047, -0.000003]</t>
+          <t>[-0.000068, -0.000011]</t>
         </is>
       </c>
     </row>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>-0.000040*</t>
+          <t>-0.000065*</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>[-0.000093, -0.000001]</t>
+          <t>[-0.000172, -0.000016]</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0.000002</t>
+          <t>-0.000015</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>[-0.000041, 0.000029]</t>
+          <t>[-0.000057, 0.000024]</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-0.000019</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>[-0.000082, 0.000025]</t>
+          <t>[-0.000105, 0.000038]</t>
         </is>
       </c>
     </row>
@@ -1318,32 +1318,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>-0.000037</t>
+          <t>-0.000099</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>[-0.000098, 0.000045]</t>
+          <t>[-0.000193, 0.000007]</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>-0.000022</t>
+          <t>-0.000026</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>[-0.000065, 0.000016]</t>
+          <t>[-0.000087, 0.000015]</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-0.000035</t>
+          <t>-0.000104</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>[-0.000136, 0.000031]</t>
+          <t>[-0.000179, 0.000025]</t>
         </is>
       </c>
     </row>
@@ -1358,32 +1358,32 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>-0.000039</t>
+          <t>-0.000146</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>[-0.000120, 0.000052]</t>
+          <t>[-0.000303, 0.000006]</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-0.000027</t>
+          <t>-0.000044</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>[-0.000072, 0.000023]</t>
+          <t>[-0.000121, 0.000007]</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-0.000054</t>
+          <t>-0.000104</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>[-0.000102, 0.000064]</t>
+          <t>[-0.000214, 0.000027]</t>
         </is>
       </c>
     </row>
@@ -1398,32 +1398,32 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>-0.000004</t>
+          <t>0.000015</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>[-0.000026, 0.000041]</t>
+          <t>[-0.000023, 0.000046]</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>-0.000006</t>
+          <t>-0.000005</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>[-0.000018, 0.000007]</t>
+          <t>[-0.000018, 0.000010]</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-0.000022*</t>
+          <t>-0.000017</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>[-0.000037, -0.000001]</t>
+          <t>[-0.000034, 0.000011]</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>[-0.000056, 0.000046]</t>
+          <t>[-0.000049, 0.000059]</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>[-0.000048, 0.000009]</t>
+          <t>[-0.000046, 0.000013]</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000015</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>[-0.000037, 0.000056]</t>
+          <t>[-0.000047, 0.000061]</t>
         </is>
       </c>
     </row>
@@ -1478,32 +1478,32 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0.000011</t>
+          <t>0.000037</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>[-0.000082, 0.000059]</t>
+          <t>[-0.000036, 0.000144]</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.000027</t>
+          <t>0.000030</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>[-0.000018, 0.000068]</t>
+          <t>[-0.000011, 0.000070]</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>0.000017</t>
+          <t>0.000021</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>[-0.000051, 0.000076]</t>
+          <t>[-0.000045, 0.000098]</t>
         </is>
       </c>
     </row>
@@ -1518,32 +1518,32 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>0.000037</t>
+          <t>0.000060</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>[-0.000078, 0.000101]</t>
+          <t>[-0.000014, 0.000195]</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>-0.000004</t>
+          <t>0.000012</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>[-0.000040, 0.000059]</t>
+          <t>[-0.000035, 0.000065]</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>0.000040</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>[-0.000128, 0.000083]</t>
+          <t>[-0.000098, 0.000113]</t>
         </is>
       </c>
     </row>
@@ -5478,13 +5478,13 @@
         <v>0.1</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>1.8e-05</v>
+        <v>-5.7e-05</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-5.5e-05</v>
+        <v>-0.00095</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.000105</v>
+        <v>5.9e-05</v>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
@@ -5510,13 +5510,13 @@
         <v>0.1</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>5.9e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>-3.7e-05</v>
+        <v>-0.000558</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>0.000142</v>
+        <v>0.000133</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -5542,13 +5542,13 @@
         <v>0.1</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-4e-05</v>
+        <v>-0.000295</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.000177</v>
+        <v>-0.000954</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>7.2e-05</v>
+        <v>0.000108</v>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
@@ -5574,13 +5574,13 @@
         <v>0.1</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>3e-06</v>
+        <v>-0.00032</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>-0.000116</v>
+        <v>-0.001555</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>0.000109</v>
+        <v>3.9e-05</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -5606,13 +5606,13 @@
         <v>0.1</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-3.7e-05</v>
+        <v>0.000177</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.000109</v>
+        <v>-0.000102</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0.000795</v>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
@@ -5638,13 +5638,13 @@
         <v>0.5</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>-3.1e-05</v>
+        <v>-4.1e-05</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>-6.499999999999999e-05</v>
+        <v>-7.7e-05</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>1.2e-05</v>
+        <v>2e-06</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
         <v>1e-05</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-9e-06</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>4.6e-05</v>
+        <v>4e-05</v>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
@@ -5702,10 +5702,10 @@
         <v>0.5</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>1e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>-3.6e-05</v>
+        <v>-7.9e-05</v>
       </c>
       <c r="G129" s="4" t="n">
         <v>3.2e-05</v>
@@ -5734,13 +5734,13 @@
         <v>0.5</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-1.1e-05</v>
+        <v>-5.6e-05</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-5.2e-05</v>
+        <v>-0.000136</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>1.7e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
@@ -5766,13 +5766,13 @@
         <v>0.5</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>-2.8e-05</v>
+        <v>-2.4e-05</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>-6.7e-05</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>0</v>
+        <v>-6.2e-05</v>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>3e-05</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -5798,13 +5798,13 @@
         <v>0.9</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-2.7e-05</v>
+        <v>-0.000163</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-9.500000000000001e-05</v>
+        <v>-0.000722</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>5.9e-05</v>
+        <v>3.4e-05</v>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
@@ -5830,13 +5830,13 @@
         <v>0.9</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>-2e-05</v>
+        <v>-0.000122</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>-7.6e-05</v>
+        <v>-0.000848</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>4.7e-05</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
@@ -5862,13 +5862,13 @@
         <v>0.9</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-3.4e-05</v>
+        <v>-7.4e-05</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.000124</v>
+        <v>-0.00039</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>4.3e-05</v>
+        <v>0.000166</v>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
@@ -5894,17 +5894,17 @@
         <v>0.9</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>-6.600000000000001e-05</v>
+        <v>-0.000359</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>-0.000195</v>
+        <v>-0.001306</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>-5e-06</v>
+        <v>3e-05</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5926,13 +5926,13 @@
         <v>0.9</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-7e-06</v>
+        <v>2.6e-05</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-9.1e-05</v>
+        <v>-0.000165</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>0.000128</v>
+        <v>0.000598</v>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0.1</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>-1e-05</v>
+        <v>-0.00038</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>-0.000326</v>
+        <v>-0.001228</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>0.00016</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>5.9e-05</v>
+        <v>-0.000221</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.000151</v>
+        <v>-0.001023</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0.000354</v>
+        <v>0.000362</v>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
@@ -6022,13 +6022,13 @@
         <v>0.1</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>-1.3e-05</v>
+        <v>-0.000656</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>-0.000331</v>
+        <v>-0.001343</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>0.000235</v>
+        <v>0.000198</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
@@ -6054,13 +6054,13 @@
         <v>0.1</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.000186</v>
+        <v>-0.000569</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>-0.000324</v>
+        <v>-0.000942</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.000109</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
@@ -6086,13 +6086,13 @@
         <v>0.1</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>-0.000129</v>
+        <v>0.000267</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>-0.000353</v>
+        <v>-0.00038</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>0.000177</v>
+        <v>0.00069</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -6118,13 +6118,13 @@
         <v>0.5</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>-8.4e-05</v>
+        <v>-0.000122</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>-0.000129</v>
+        <v>-0.00022</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>5e-05</v>
+        <v>1.7e-05</v>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
@@ -6150,13 +6150,13 @@
         <v>0.5</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>4e-06</v>
+        <v>-2.4e-05</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>-8.8e-05</v>
+        <v>-0.000126</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>5.4e-05</v>
+        <v>5.1e-05</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -6182,13 +6182,13 @@
         <v>0.5</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>5e-06</v>
+        <v>-5.6e-05</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>-0.000115</v>
+        <v>-0.00025</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>6.1e-05</v>
+        <v>2.3e-05</v>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
@@ -6214,13 +6214,13 @@
         <v>0.5</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>-3.7e-05</v>
+        <v>-0.000111</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>-0.000137</v>
+        <v>-0.000306</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>9.2e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
@@ -6246,17 +6246,17 @@
         <v>0.5</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>-0.000153</v>
+        <v>-9.1e-05</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>-0.000201</v>
+        <v>-0.000191</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>-1.3e-05</v>
+        <v>5.5e-05</v>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6278,13 +6278,13 @@
         <v>0.9</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>1.5e-05</v>
+        <v>-0.000204</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>-0.000151</v>
+        <v>-0.0009990000000000001</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>0.000178</v>
+        <v>0.000109</v>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
@@ -6310,13 +6310,13 @@
         <v>0.9</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>-2.6e-05</v>
+        <v>-0.000301</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>-0.000258</v>
+        <v>-0.00103</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>0.000121</v>
+        <v>5.4e-05</v>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         <v>0.9</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>8.6e-05</v>
+        <v>-0.000171</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>-0.000195</v>
+        <v>-0.001081</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>0.00014</v>
+        <v>9.2e-05</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
@@ -6374,13 +6374,13 @@
         <v>0.9</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>-1.8e-05</v>
+        <v>-0.000359</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>-0.000294</v>
+        <v>-0.001024</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>8.6e-05</v>
+        <v>0.000359</v>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
@@ -6406,13 +6406,13 @@
         <v>0.9</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>-0.000111</v>
+        <v>-0.000102</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>-0.000229</v>
+        <v>-0.00042</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>9.2e-05</v>
+        <v>0.000445</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -6438,13 +6438,13 @@
         <v>0.1</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>2e-05</v>
+        <v>-0.000449</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>-0.000447</v>
+        <v>-0.001047</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>0.000252</v>
+        <v>0.000228</v>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
@@ -6470,13 +6470,13 @@
         <v>0.1</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>-1e-05</v>
+        <v>-0.00032</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>-0.000273</v>
+        <v>-0.000884</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>0.000362</v>
+        <v>0.000271</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -6502,13 +6502,13 @@
         <v>0.1</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>0.000103</v>
+        <v>-0.0009940000000000001</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>-0.000188</v>
+        <v>-0.0019</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>0.0005240000000000001</v>
+        <v>0.000271</v>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
@@ -6534,13 +6534,13 @@
         <v>0.1</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>2e-05</v>
+        <v>-0.000388</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>-0.000265</v>
+        <v>-0.001062</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>0.000334</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
@@ -6566,13 +6566,13 @@
         <v>0.1</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>-0.000206</v>
+        <v>0.000888</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>-0.000603</v>
+        <v>-0.000476</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>0.000325</v>
+        <v>0.001439</v>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         <v>0.5</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>6e-06</v>
+        <v>-8.1e-05</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>-0.000121</v>
+        <v>-0.000201</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>0.000162</v>
+        <v>0.000117</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -6630,13 +6630,13 @@
         <v>0.5</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>1.1e-05</v>
+        <v>-5.5e-05</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>-0.00011</v>
+        <v>-0.000173</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>4e-05</v>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
@@ -6662,13 +6662,13 @@
         <v>0.5</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>-1.8e-05</v>
+        <v>-0.000103</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>-0.000172</v>
+        <v>-0.00042</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>0.000135</v>
+        <v>2.8e-05</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -6694,13 +6694,13 @@
         <v>0.5</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>-3.2e-05</v>
+        <v>-9.500000000000001e-05</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>-0.000139</v>
+        <v>-0.000282</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>0.000112</v>
+        <v>8.000000000000001e-05</v>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
@@ -6726,13 +6726,13 @@
         <v>0.5</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>-0.000116</v>
+        <v>-3.1e-05</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>-0.000213</v>
+        <v>-0.000141</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>4.6e-05</v>
+        <v>0.000196</v>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
@@ -6758,13 +6758,13 @@
         <v>0.9</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>8.7e-05</v>
+        <v>8e-06</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>-2.7e-05</v>
+        <v>-0.000541</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>0.000479</v>
+        <v>0.000313</v>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
@@ -6790,13 +6790,13 @@
         <v>0.9</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>-5.1e-05</v>
+        <v>-0.000179</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>-0.000303</v>
+        <v>-0.001023</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>0.000127</v>
+        <v>0.000148</v>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
@@ -6822,13 +6822,13 @@
         <v>0.9</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>4.5e-05</v>
+        <v>-0.000353</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>-0.000196</v>
+        <v>-0.001376</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>0.000336</v>
+        <v>9.1e-05</v>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
@@ -6854,13 +6854,13 @@
         <v>0.9</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>-0.000117</v>
+        <v>-0.00038</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>-0.000342</v>
+        <v>-0.000785</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>0.000111</v>
+        <v>0.000236</v>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
@@ -6886,13 +6886,13 @@
         <v>0.9</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>-6.4e-05</v>
+        <v>0.000374</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>-0.000346</v>
+        <v>-0.000227</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>0.000326</v>
+        <v>0.001046</v>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
@@ -6918,13 +6918,13 @@
         <v>0.1</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>0.00017</v>
+        <v>-0.000227</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>-0.00028</v>
+        <v>-0.001303</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>0.00035</v>
+        <v>0.000332</v>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
@@ -6950,13 +6950,13 @@
         <v>0.1</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>0.000202</v>
+        <v>5.5e-05</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>-0.000295</v>
+        <v>-0.000643</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>0.000751</v>
+        <v>0.000653</v>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
@@ -6982,13 +6982,13 @@
         <v>0.1</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>0.000185</v>
+        <v>-0.001465</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>-0.000511</v>
+        <v>-0.002457</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>0.000614</v>
+        <v>0.000225</v>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
@@ -7014,13 +7014,13 @@
         <v>0.1</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>-0.000103</v>
+        <v>-0.000728</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>-0.000355</v>
+        <v>-0.002079</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>0.000443</v>
+        <v>0.000237</v>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
@@ -7046,13 +7046,13 @@
         <v>0.1</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>-0.0002</v>
+        <v>0.000828</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>-0.000626</v>
+        <v>-0.000328</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>0.000653</v>
+        <v>0.001828</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
@@ -7078,13 +7078,13 @@
         <v>0.5</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>-4.3e-05</v>
+        <v>-0.000144</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>-0.00026</v>
+        <v>-0.000431</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>0.00023</v>
+        <v>0.000137</v>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
@@ -7110,13 +7110,13 @@
         <v>0.5</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>-9.6e-05</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>-0.000222</v>
+        <v>-0.00027</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>5.9e-05</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -7142,13 +7142,13 @@
         <v>0.5</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>-4.9e-05</v>
+        <v>-0.000152</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>-0.000183</v>
+        <v>-0.000589</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>0.00011</v>
+        <v>3.3e-05</v>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
@@ -7174,13 +7174,13 @@
         <v>0.5</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>5e-05</v>
+        <v>-0.000248</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>-0.000183</v>
+        <v>-0.000606</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.000201</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -7206,13 +7206,13 @@
         <v>0.5</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>-0.000141</v>
+        <v>-3.1e-05</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>-0.000312</v>
+        <v>-0.000229</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>6.8e-05</v>
+        <v>0.000392</v>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
@@ -7238,13 +7238,13 @@
         <v>0.9</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>0.000267</v>
+        <v>-0.000276</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>-0.000139</v>
+        <v>-0.0009300000000000001</v>
       </c>
       <c r="G177" s="4" t="n">
-        <v>0.000654</v>
+        <v>0.000487</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -7270,13 +7270,13 @@
         <v>0.9</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>-4.1e-05</v>
+        <v>-0.000164</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>-0.000467</v>
+        <v>-0.00101</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>0.000205</v>
+        <v>0.000245</v>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
@@ -7302,13 +7302,13 @@
         <v>0.9</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>3.1e-05</v>
+        <v>-0.00043</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>-0.000262</v>
+        <v>-0.001315</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>0.000448</v>
+        <v>0.000106</v>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
@@ -7333,14 +7333,14 @@
       <c r="D180" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="E180" s="5" t="n">
-        <v>0</v>
+      <c r="E180" s="4" t="n">
+        <v>-0.000821</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>-0.00023</v>
+        <v>-0.0015</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>0.000477</v>
+        <v>0.00026</v>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
@@ -7366,13 +7366,13 @@
         <v>0.9</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>-0.000112</v>
+        <v>0.000398</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>-0.000468</v>
+        <v>-0.000224</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>0.00023</v>
+        <v>0.001238</v>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>h1-q0.90</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Significant responses present at listed horizon-quantile pairs.</t>
+          <t>No significant dynamic responses.</t>
         </is>
       </c>
     </row>
@@ -7743,12 +7743,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>h5-q0.50</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Significant responses present at listed horizon-quantile pairs.</t>
+          <t>No significant dynamic responses.</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -7819,22 +7819,22 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.000394</v>
+        <v>0.002192</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.002766</v>
+        <v>-0.041089</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>-1e-06</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.003251</v>
+        <v>0.032109</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="3">
@@ -7844,22 +7844,22 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.000394</v>
+        <v>0.000303</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1.697329</v>
+        <v>1.689697</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>-11.8979</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.0955</v>
+        <v>-0.0929</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>17.7581</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="4">
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.000226</v>
+        <v>0.000272</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.043947</v>
+        <v>0.043996</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>-0.29</v>
@@ -7884,7 +7884,7 @@
         <v>0.298</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="5">
@@ -7894,22 +7894,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8.7e-05</v>
+        <v>0.000179</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.040253</v>
+        <v>0.041009</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>-0.352421</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.000489</v>
+        <v>-0.000457</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0.412784</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="6">
@@ -7919,22 +7919,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.000182</v>
+        <v>-8.3e-05</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.022937</v>
+        <v>0.023741</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>-0.279761</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.000757</v>
+        <v>0.000828</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0.190774</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="7">
@@ -7944,22 +7944,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.000671</v>
+        <v>0.000637</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.030645</v>
+        <v>0.030478</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>-0.432421</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.000837</v>
+        <v>0.000753</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>0.23923</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>3526</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="9">
@@ -8039,19 +8039,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.042</v>
+        <v>0.061</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.021</v>
+        <v>0.099</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.048</v>
+        <v>0.095</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.019</v>
       </c>
     </row>
     <row r="3">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-0.042</v>
+        <v>0.061</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.179</v>
+        <v>-0.164</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>-0.228</v>
+        <v>-0.195</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.171</v>
+        <v>-0.173</v>
       </c>
     </row>
     <row r="4">
@@ -8086,22 +8086,22 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.021</v>
+        <v>0.099</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.179</v>
+        <v>-0.164</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.027</v>
+        <v>-0.006</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.145</v>
+        <v>0.161</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -8111,22 +8111,22 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-0.048</v>
+        <v>0.095</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.027</v>
+        <v>-0.006</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.139</v>
+        <v>0.171</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.193</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="6">
@@ -8136,22 +8136,22 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.228</v>
+        <v>-0.195</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.145</v>
+        <v>0.161</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.139</v>
+        <v>0.171</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.156</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="7">
@@ -8161,19 +8161,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.019</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.171</v>
+        <v>-0.173</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.193</v>
+        <v>0.181</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.156</v>
+        <v>0.141</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1.105</v>
+        <v>1.091</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1.06</v>
+        <v>1.068</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1.084</v>
+        <v>1.077</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -8322,13 +8322,13 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8396,52 +8396,52 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>-0.000009</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000035, 0.000000]</t>
+          <t>[-0.000027, 0.000010]</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>-0.000018*</t>
+          <t>-0.000012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000033, -0.000002]</t>
+          <t>[-0.000026, 0.000006]</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>-0.000014*</t>
+          <t>-0.000011</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000027, -0.000001]</t>
+          <t>[-0.000024, 0.000005]</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>-0.000003</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000020, 0.000003]</t>
+          <t>[-0.000016, 0.000010]</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>-0.000005</t>
+          <t>0.000007</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000024, 0.000012]</t>
+          <t>[-0.000016, 0.000039]</t>
         </is>
       </c>
     </row>
@@ -8453,52 +8453,52 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0.000238</t>
+          <t>0.000727</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000307, 0.000791]</t>
+          <t>[-0.000024, 0.001417]</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.000334</t>
+          <t>0.000488</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000120, 0.000808]</t>
+          <t>[-0.000013, 0.001046]</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>0.000280</t>
+          <t>0.000352*</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000115, 0.000641]</t>
+          <t>[0.000005, 0.000764]</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>0.000401*</t>
+          <t>0.000509*</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>[0.000046, 0.000745]</t>
+          <t>[0.000148, 0.000923]</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>0.000299</t>
+          <t>0.000520</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000221, 0.000761]</t>
+          <t>[-0.000005, 0.001501]</t>
         </is>
       </c>
     </row>
@@ -8510,52 +8510,52 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.000169</t>
+          <t>0.000361</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000487, 0.000641]</t>
+          <t>[-0.000244, 0.001097]</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>-0.000092</t>
+          <t>0.000064</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000514, 0.000314]</t>
+          <t>[-0.000401, 0.000547]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>-0.000196</t>
+          <t>-0.000112</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000466, 0.000104]</t>
+          <t>[-0.000435, 0.000193]</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>-0.000245</t>
+          <t>-0.000047</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000745, 0.000077]</t>
+          <t>[-0.000717, 0.000295]</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-0.000453</t>
+          <t>-0.000064</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>[-0.001156, 0.000033]</t>
+          <t>[-0.001096, 0.001167]</t>
         </is>
       </c>
     </row>
@@ -8567,52 +8567,52 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>-0.000567</t>
+          <t>0.000230</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[-0.002567, 0.000707]</t>
+          <t>[-0.002190, 0.001796]</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>-0.000946*</t>
+          <t>-0.000758</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[-0.001669, -0.000037]</t>
+          <t>[-0.001367, 0.000669]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>-0.000793*</t>
+          <t>-0.000580</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[-0.001458, -0.000161]</t>
+          <t>[-0.001296, 0.000209]</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>-0.001257*</t>
+          <t>-0.000745</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[-0.002014, -0.000260]</t>
+          <t>[-0.001758, 0.000646]</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-0.001728*</t>
+          <t>-0.000598</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[-0.002576, -0.000046]</t>
+          <t>[-0.002110, 0.002208]</t>
         </is>
       </c>
     </row>
@@ -8624,52 +8624,52 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>0.000639</t>
+          <t>0.000055</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000614, 0.001271]</t>
+          <t>[-0.001013, 0.001057]</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.000354</t>
+          <t>0.000303</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000397, 0.000914]</t>
+          <t>[-0.000488, 0.000897]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0.000010</t>
+          <t>-0.000130</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000429, 0.000465]</t>
+          <t>[-0.000523, 0.000373]</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>0.000025</t>
+          <t>-0.000080</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000428, 0.000530]</t>
+          <t>[-0.000575, 0.000461]</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0.000084</t>
+          <t>0.000098</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000459, 0.000915]</t>
+          <t>[-0.001180, 0.000714]</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0.0052</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="3">
@@ -8723,7 +8723,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.0057</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="4">
@@ -8731,7 +8731,7 @@
         <v>0.5</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0052</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="5">
@@ -8739,7 +8739,7 @@
         <v>0.75</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.0052</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="6">
@@ -8747,7 +8747,7 @@
         <v>0.9</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0063</v>
+        <v>0.001</v>
       </c>
     </row>
   </sheetData>
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-2e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.732</v>
+        <v>0.83</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>3.4e-05</v>
+        <v>0.000267</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.878</v>
+        <v>0.388</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -8865,14 +8865,14 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.000395</v>
+        <v>0.0005509999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.174</v>
+        <v>0.048</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.000177</v>
+        <v>0.000599</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.736</v>
+        <v>0.432</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.000369</v>
+        <v>8.4e-05</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.418</v>
+        <v>0.854</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -8937,10 +8937,10 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.1e-05</v>
+        <v>-1.6e-05</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.3e-05</v>
+        <v>4e-05</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.968</v>
+        <v>0.9</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.000711</v>
+        <v>0.000476</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.000759</v>
+        <v>0.000393</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.426</v>
+        <v>0.648</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.000177</v>
+        <v>6.3e-05</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.732</v>
+        <v>0.962</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9057,14 +9057,14 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-9e-06</v>
+        <v>-1.8e-05</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.214</v>
+        <v>0.042</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -9081,10 +9081,10 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.1e-05</v>
+        <v>-0.000228</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.504</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.000317</v>
+        <v>-7.4e-05</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.204</v>
+        <v>0.958</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.0005820000000000001</v>
+        <v>-0.000207</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.226</v>
+        <v>0.87</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.000193</v>
+        <v>-2.1e-05</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.55</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -9235,8 +9235,8 @@
       <c r="A2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>0.00111</v>
+      <c r="B2" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>0</v>
@@ -9264,8 +9264,8 @@
       <c r="A3" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>0.00149</v>
+      <c r="B3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
@@ -9293,8 +9293,8 @@
       <c r="A4" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>0.00129</v>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -9322,8 +9322,8 @@
       <c r="A5" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>0.00139</v>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -9351,8 +9351,8 @@
       <c r="A6" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0.00141</v>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>q0.10, q0.25, q0.50, q0.75, q0.90</t>
+          <t>q0.25, q0.50, q0.75, q0.90</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>q0.10, q0.25, q0.50</t>
+          <t>q0.25</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>q0.25, q0.50, q0.75, q0.90</t>
+          <t>q0.25, q0.75</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>q0.25, q0.50, q0.75</t>
+          <t>q0.50, q0.75</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -9741,17 +9741,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>q0.10</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Negative effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>
@@ -9768,17 +9768,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>q0.75</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Negative effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>
@@ -9795,17 +9795,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>q0.10, q0.90</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Negative effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>
@@ -9822,17 +9822,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>q0.90</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Positive effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>

--- a/final_outputs/final_tables_formatted.xlsx
+++ b/final_outputs/final_tables_formatted.xlsx
@@ -493,7 +493,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-13.5226</v>
+        <v>-11.8082</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-212.0164</v>
+        <v>-60.6926</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,32 +758,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>0.000015</t>
+          <t>0.000025</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000037, 0.000036]</t>
+          <t>[-0.000005, 0.000044]</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>-0.000006</t>
+          <t>-0.000002</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000021, 0.000008]</t>
+          <t>[-0.000017, 0.000014]</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>-0.000018</t>
+          <t>-0.000009</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000046, 0.000011]</t>
+          <t>[-0.000034, 0.000023]</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>0.000014</t>
+          <t>0.000035</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000068, 0.000060]</t>
+          <t>[-0.000028, 0.000071]</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>0.000001</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000039, 0.000029]</t>
+          <t>[-0.000034, 0.000036]</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>0.000009</t>
+          <t>0.000013</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000055, 0.000068]</t>
+          <t>[-0.000041, 0.000068]</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>0.000030</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000107, 0.000088]</t>
+          <t>[-0.000052, 0.000103]</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.000006</t>
+          <t>0.000013</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000042, 0.000051]</t>
+          <t>[-0.000038, 0.000058]</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000013</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000060, 0.000098]</t>
+          <t>[-0.000041, 0.000109]</t>
         </is>
       </c>
     </row>
@@ -878,32 +878,32 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>0.000027</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[-0.000104, 0.000071]</t>
+          <t>[-0.000074, 0.000090]</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.000031</t>
+          <t>0.000033</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[-0.000041, 0.000084]</t>
+          <t>[-0.000024, 0.000084]</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-0.000026</t>
+          <t>0.000025</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[-0.000115, 0.000080]</t>
+          <t>[-0.000067, 0.000088]</t>
         </is>
       </c>
     </row>
@@ -918,32 +918,32 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>-0.000009</t>
+          <t>0.000007</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000039, 0.000020]</t>
+          <t>[-0.000027, 0.000030]</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0.000003</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000011, 0.000016]</t>
+          <t>[-0.000007, 0.000019]</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-0.000007</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000017]</t>
+          <t>[-0.000016, 0.000028]</t>
         </is>
       </c>
     </row>
@@ -958,32 +958,32 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>0.000012</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>[-0.000076, 0.000046]</t>
+          <t>[-0.000037, 0.000060]</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0.000009</t>
+          <t>0.000019</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>[-0.000019, 0.000045]</t>
+          <t>[-0.000011, 0.000048]</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-0.000027</t>
+          <t>-0.000011</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>[-0.000077, 0.000048]</t>
+          <t>[-0.000057, 0.000063]</t>
         </is>
       </c>
     </row>
@@ -998,32 +998,32 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>-0.000063</t>
+          <t>-0.000048</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>[-0.000140, 0.000029]</t>
+          <t>[-0.000095, 0.000053]</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000004</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>[-0.000047, 0.000035]</t>
+          <t>[-0.000038, 0.000040]</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-0.000034</t>
+          <t>-0.000028</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>[-0.000087, 0.000033]</t>
+          <t>[-0.000076, 0.000044]</t>
         </is>
       </c>
     </row>
@@ -1038,32 +1038,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>-0.000013</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>[-0.000098, 0.000061]</t>
+          <t>[-0.000072, 0.000088]</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-0.000064</t>
+          <t>-0.000046</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>[-0.000108, 0.000002]</t>
+          <t>[-0.000096, 0.000006]</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-0.000021</t>
+          <t>0.000005</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>[-0.000112, 0.000048]</t>
+          <t>[-0.000100, 0.000051]</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>[-0.000063, 0.000005]</t>
+          <t>[-0.000051, 0.000003]</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1093,17 +1093,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>[-0.000017, 0.000006]</t>
+          <t>[-0.000016, 0.000009]</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-0.000034</t>
+          <t>-0.000018</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>[-0.000062, 0.000006]</t>
+          <t>[-0.000045, 0.000016]</t>
         </is>
       </c>
     </row>
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>-0.000038</t>
+          <t>-0.000020</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>[-0.000127, 0.000040]</t>
+          <t>[-0.000078, 0.000037]</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-0.000014</t>
+          <t>-0.000002</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>[-0.000039, 0.000011]</t>
+          <t>[-0.000028, 0.000017]</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-0.000040</t>
+          <t>-0.000003</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>[-0.000107, 0.000024]</t>
+          <t>[-0.000071, 0.000045]</t>
         </is>
       </c>
     </row>
@@ -1158,32 +1158,32 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>-0.000036</t>
+          <t>-0.000023</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>[-0.000183, 0.000036]</t>
+          <t>[-0.000089, 0.000060]</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>-0.000011</t>
+          <t>0.000006</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>[-0.000058, 0.000051]</t>
+          <t>[-0.000042, 0.000061]</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-0.000036</t>
+          <t>-0.000010</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>[-0.000149, 0.000038]</t>
+          <t>[-0.000076, 0.000067]</t>
         </is>
       </c>
     </row>
@@ -1198,32 +1198,32 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>-0.000005</t>
+          <t>0.000027</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>[-0.000187, 0.000068]</t>
+          <t>[-0.000090, 0.000099]</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0.000005</t>
+          <t>0.000023</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>[-0.000054, 0.000065]</t>
+          <t>[-0.000029, 0.000072]</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-0.000038</t>
+          <t>-0.000025</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>[-0.000151, 0.000001]</t>
+          <t>[-0.000122, 0.000016]</t>
         </is>
       </c>
     </row>
@@ -1238,32 +1238,32 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0.000003</t>
+          <t>0.000024</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>[-0.000068, 0.000026]</t>
+          <t>[-0.000010, 0.000045]</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>-0.000016</t>
+          <t>-0.000010</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>[-0.000031, 0.000004]</t>
+          <t>[-0.000023, 0.000012]</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-0.000032*</t>
+          <t>-0.000021</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>[-0.000068, -0.000011]</t>
+          <t>[-0.000042, 0.000012]</t>
         </is>
       </c>
     </row>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>-0.000065*</t>
+          <t>-0.000050*</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>[-0.000172, -0.000016]</t>
+          <t>[-0.000155, -0.000013]</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-0.000015</t>
+          <t>-0.000007</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>[-0.000057, 0.000024]</t>
+          <t>[-0.000049, 0.000024]</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-0.000012</t>
+          <t>-0.000029</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>[-0.000105, 0.000038]</t>
+          <t>[-0.000090, 0.000021]</t>
         </is>
       </c>
     </row>
@@ -1318,32 +1318,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>-0.000099</t>
+          <t>-0.000061</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>[-0.000193, 0.000007]</t>
+          <t>[-0.000188, 0.000034]</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>-0.000026</t>
+          <t>-0.000028</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>[-0.000087, 0.000015]</t>
+          <t>[-0.000079, 0.000018]</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-0.000104</t>
+          <t>-0.000063</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>[-0.000179, 0.000025]</t>
+          <t>[-0.000155, 0.000031]</t>
         </is>
       </c>
     </row>
@@ -1358,32 +1358,32 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>-0.000146</t>
+          <t>-0.000048</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>[-0.000303, 0.000006]</t>
+          <t>[-0.000156, 0.000060]</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-0.000044</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>[-0.000121, 0.000007]</t>
+          <t>[-0.000084, 0.000012]</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-0.000104</t>
+          <t>-0.000034</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>[-0.000214, 0.000027]</t>
+          <t>[-0.000135, 0.000054]</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>0.000015</t>
+          <t>0.000008</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>[-0.000023, 0.000046]</t>
+          <t>[-0.000020, 0.000045]</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>[-0.000018, 0.000010]</t>
+          <t>[-0.000018, 0.000008]</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-0.000017</t>
+          <t>-0.000025</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>[-0.000034, 0.000011]</t>
+          <t>[-0.000040, 0.000000]</t>
         </is>
       </c>
     </row>
@@ -1438,19 +1438,19 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t>-0.000015</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>[-0.000051, 0.000050]</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
           <t>-0.000022</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>[-0.000049, 0.000059]</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>-0.000023</t>
-        </is>
-      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>[-0.000046, 0.000013]</t>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>0.000015</t>
+          <t>0.000017</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>[-0.000047, 0.000061]</t>
+          <t>[-0.000053, 0.000056]</t>
         </is>
       </c>
     </row>
@@ -1478,32 +1478,32 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0.000037</t>
+          <t>0.000016</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>[-0.000036, 0.000144]</t>
+          <t>[-0.000053, 0.000120]</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.000030</t>
+          <t>0.000029</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>[-0.000011, 0.000070]</t>
+          <t>[-0.000020, 0.000073]</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>0.000021</t>
+          <t>0.000010</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>[-0.000045, 0.000098]</t>
+          <t>[-0.000049, 0.000082]</t>
         </is>
       </c>
     </row>
@@ -1518,32 +1518,32 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>0.000060</t>
+          <t>0.000039</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>[-0.000014, 0.000195]</t>
+          <t>[-0.000078, 0.000104]</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>0.000012</t>
+          <t>0.000000</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>[-0.000035, 0.000065]</t>
+          <t>[-0.000037, 0.000061]</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>0.000040</t>
+          <t>-0.000006</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>[-0.000098, 0.000113]</t>
+          <t>[-0.000129, 0.000088]</t>
         </is>
       </c>
     </row>
@@ -5478,13 +5478,13 @@
         <v>0.1</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-5.7e-05</v>
+        <v>2.2e-05</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.00095</v>
+        <v>-5.9e-05</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>5.9e-05</v>
+        <v>0.000147</v>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
@@ -5510,13 +5510,13 @@
         <v>0.1</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>3e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>-0.000558</v>
+        <v>-5.9e-05</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>0.000133</v>
+        <v>0.000167</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -5542,13 +5542,13 @@
         <v>0.1</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.000295</v>
+        <v>-0.000125</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.000954</v>
+        <v>-0.000194</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>0.000108</v>
+        <v>3.7e-05</v>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
@@ -5574,13 +5574,13 @@
         <v>0.1</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>-0.00032</v>
+        <v>6.4e-05</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>-0.001555</v>
+        <v>-9.3e-05</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>3.9e-05</v>
+        <v>0.000145</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -5606,13 +5606,13 @@
         <v>0.1</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>0.000177</v>
+        <v>2.3e-05</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.000102</v>
+        <v>-6.9e-05</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.000795</v>
+        <v>0.000148</v>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
@@ -5638,13 +5638,13 @@
         <v>0.5</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>-4.1e-05</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>-7.7e-05</v>
+        <v>-5.3e-05</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>2e-06</v>
+        <v>2.9e-05</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
@@ -5670,13 +5670,13 @@
         <v>0.5</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>1e-05</v>
+        <v>1.8e-05</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-2.2e-05</v>
+        <v>-9e-06</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>4e-05</v>
+        <v>5.4e-05</v>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
@@ -5702,13 +5702,13 @@
         <v>0.5</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>-2e-06</v>
+        <v>-8e-06</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>-7.9e-05</v>
+        <v>-3.8e-05</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>3.2e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
@@ -5734,13 +5734,13 @@
         <v>0.5</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-5.6e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.000136</v>
+        <v>-6.499999999999999e-05</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>5e-06</v>
+        <v>5e-05</v>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
@@ -5766,13 +5766,13 @@
         <v>0.5</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>-2.4e-05</v>
+        <v>-2.3e-05</v>
       </c>
       <c r="F131" s="4" t="n">
         <v>-6.2e-05</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>3e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -5798,13 +5798,13 @@
         <v>0.9</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.000163</v>
+        <v>2.3e-05</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.000722</v>
+        <v>-9.1e-05</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>3.4e-05</v>
+        <v>0.000154</v>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
@@ -5830,13 +5830,13 @@
         <v>0.9</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>-0.000122</v>
+        <v>6.9e-05</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>-0.000848</v>
+        <v>-8.4e-05</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>4.7e-05</v>
+        <v>0.000155</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
@@ -5862,13 +5862,13 @@
         <v>0.9</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-7.4e-05</v>
+        <v>4.7e-05</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.00039</v>
+        <v>-0.000128</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.000166</v>
+        <v>0.0001</v>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         <v>0.9</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>-0.000359</v>
+        <v>-2.6e-05</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>-0.001306</v>
+        <v>-0.000179</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>3e-05</v>
+        <v>0.000166</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -5926,13 +5926,13 @@
         <v>0.9</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2.6e-05</v>
+        <v>-2.9e-05</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.000165</v>
+        <v>-0.000104</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>0.000598</v>
+        <v>0.000151</v>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0.1</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>-0.00038</v>
+        <v>-4e-06</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>-0.001228</v>
+        <v>-0.000328</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>0.000146</v>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
@@ -5990,13 +5990,13 @@
         <v>0.1</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.000221</v>
+        <v>7.1e-05</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.001023</v>
+        <v>-0.000261</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0.000362</v>
+        <v>0.000382</v>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
@@ -6022,13 +6022,13 @@
         <v>0.1</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>-0.000656</v>
+        <v>-0.000139</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>-0.001343</v>
+        <v>-0.000328</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>0.000198</v>
+        <v>0.000244</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
@@ -6054,13 +6054,13 @@
         <v>0.1</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.000569</v>
+        <v>-0.000301</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>-0.000942</v>
+        <v>-0.000583</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>4.6e-05</v>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
@@ -6086,13 +6086,13 @@
         <v>0.1</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>0.000267</v>
+        <v>4.2e-05</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>-0.00038</v>
+        <v>-0.000307</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>0.00069</v>
+        <v>0.000393</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -6118,13 +6118,13 @@
         <v>0.5</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>-0.000122</v>
+        <v>-9.399999999999999e-05</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>-0.00022</v>
+        <v>-0.000148</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>1.7e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
@@ -6150,13 +6150,13 @@
         <v>0.5</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>-2.4e-05</v>
+        <v>-1.5e-05</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>-0.000126</v>
+        <v>-8.4e-05</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>5.1e-05</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -6182,13 +6182,13 @@
         <v>0.5</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>-5.6e-05</v>
+        <v>-2.3e-05</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>-0.00025</v>
+        <v>-0.000123</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>2.3e-05</v>
+        <v>6.1e-05</v>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
@@ -6214,13 +6214,13 @@
         <v>0.5</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>-0.000111</v>
+        <v>-7.4e-05</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>-0.000306</v>
+        <v>-0.000205</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.000111</v>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
@@ -6246,13 +6246,13 @@
         <v>0.5</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>-9.1e-05</v>
+        <v>-0.000126</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>-0.000191</v>
+        <v>-0.000202</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>5.5e-05</v>
+        <v>1.6e-05</v>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
@@ -6278,13 +6278,13 @@
         <v>0.9</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>-0.000204</v>
+        <v>-5e-06</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>-0.0009990000000000001</v>
+        <v>-0.000199</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>0.000109</v>
+        <v>0.000163</v>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
@@ -6310,13 +6310,13 @@
         <v>0.9</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>-0.000301</v>
+        <v>1.6e-05</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>-0.00103</v>
+        <v>-0.000262</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>5.4e-05</v>
+        <v>0.000152</v>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         <v>0.9</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>-0.000171</v>
+        <v>5.2e-05</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>-0.001081</v>
+        <v>-0.000207</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>9.2e-05</v>
+        <v>0.000152</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
@@ -6374,13 +6374,13 @@
         <v>0.9</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>-0.000359</v>
+        <v>-0.000163</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>-0.001024</v>
+        <v>-0.000323</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>0.000359</v>
+        <v>7.2e-05</v>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
@@ -6406,13 +6406,13 @@
         <v>0.9</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>-0.000102</v>
+        <v>-0.000144</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>-0.00042</v>
+        <v>-0.000284</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>0.000445</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -6438,13 +6438,13 @@
         <v>0.1</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>-0.000449</v>
+        <v>6.7e-05</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>-0.001047</v>
+        <v>-0.000622</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>0.000228</v>
+        <v>0.000287</v>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
@@ -6470,13 +6470,13 @@
         <v>0.1</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>-0.00032</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>-0.000884</v>
+        <v>-0.000343</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>0.000271</v>
+        <v>0.00042</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -6502,13 +6502,13 @@
         <v>0.1</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>-0.0009940000000000001</v>
+        <v>-0.000287</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>-0.0019</v>
+        <v>-0.000585</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>0.000271</v>
+        <v>0.000407</v>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
@@ -6534,13 +6534,13 @@
         <v>0.1</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>-0.000388</v>
+        <v>-0.000189</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>-0.001062</v>
+        <v>-0.000534</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>9.399999999999999e-05</v>
+        <v>0.000324</v>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
@@ -6566,13 +6566,13 @@
         <v>0.1</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>0.000888</v>
+        <v>0.000144</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>-0.000476</v>
+        <v>-0.000483</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>0.001439</v>
+        <v>0.00051</v>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         <v>0.5</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>-8.1e-05</v>
+        <v>-1.6e-05</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>-0.000201</v>
+        <v>-0.000128</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>0.000117</v>
+        <v>0.000203</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -6630,13 +6630,13 @@
         <v>0.5</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>-5.5e-05</v>
+        <v>-7e-06</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>-0.000173</v>
+        <v>-0.00012</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>4e-05</v>
+        <v>8.1e-05</v>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
@@ -6662,13 +6662,13 @@
         <v>0.5</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>-0.000103</v>
+        <v>-4.5e-05</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>-0.00042</v>
+        <v>-0.000232</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>2.8e-05</v>
+        <v>7.8e-05</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -6694,13 +6694,13 @@
         <v>0.5</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>-9.500000000000001e-05</v>
+        <v>-5.9e-05</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>-0.000282</v>
+        <v>-0.0002</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>0.000114</v>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
@@ -6726,13 +6726,13 @@
         <v>0.5</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>-3.1e-05</v>
+        <v>-7.1e-05</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>-0.000141</v>
+        <v>-0.000187</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>0.000196</v>
+        <v>9.1e-05</v>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
@@ -6758,13 +6758,13 @@
         <v>0.9</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>8e-06</v>
+        <v>0.000207</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>-0.000541</v>
+        <v>-0.000166</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>0.000313</v>
+        <v>0.000457</v>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
@@ -6790,13 +6790,13 @@
         <v>0.9</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>-0.000179</v>
+        <v>4.2e-05</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>-0.001023</v>
+        <v>-0.000283</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>0.000148</v>
+        <v>0.000236</v>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
@@ -6822,13 +6822,13 @@
         <v>0.9</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>-0.000353</v>
+        <v>3.5e-05</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>-0.001376</v>
+        <v>-0.00038</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>9.1e-05</v>
+        <v>0.000251</v>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
@@ -6854,13 +6854,13 @@
         <v>0.9</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>-0.00038</v>
+        <v>-0.000217</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>-0.000785</v>
+        <v>-0.00051</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>0.000236</v>
+        <v>9.1e-05</v>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
@@ -6886,13 +6886,13 @@
         <v>0.9</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>0.000374</v>
+        <v>-3.8e-05</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>-0.000227</v>
+        <v>-0.000243</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>0.001046</v>
+        <v>0.000319</v>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
@@ -6918,13 +6918,13 @@
         <v>0.1</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>-0.000227</v>
+        <v>-4e-06</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>-0.001303</v>
+        <v>-0.000448</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>0.000332</v>
+        <v>0.000392</v>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
@@ -6950,13 +6950,13 @@
         <v>0.1</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>5.5e-05</v>
+        <v>0.000417</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>-0.000643</v>
+        <v>-0.000245</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>0.000653</v>
+        <v>0.001012</v>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
@@ -6982,13 +6982,13 @@
         <v>0.1</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>-0.001465</v>
+        <v>-7e-06</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>-0.002457</v>
+        <v>-0.000902</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>0.000225</v>
+        <v>0.000612</v>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
@@ -7014,13 +7014,13 @@
         <v>0.1</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>-0.000728</v>
+        <v>-0.000225</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>-0.002079</v>
+        <v>-0.001063</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>0.000237</v>
+        <v>0.000476</v>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
@@ -7046,13 +7046,13 @@
         <v>0.1</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>0.000828</v>
+        <v>0.000448</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>-0.000328</v>
+        <v>-0.000518</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>0.001828</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
@@ -7078,13 +7078,13 @@
         <v>0.5</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>-0.000144</v>
+        <v>-7.1e-05</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>-0.000431</v>
+        <v>-0.000391</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>0.000137</v>
+        <v>0.000171</v>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
@@ -7110,13 +7110,13 @@
         <v>0.5</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>-7.3e-05</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>-0.00027</v>
+        <v>-0.000228</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>9.399999999999999e-05</v>
+        <v>0.000104</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -7142,13 +7142,13 @@
         <v>0.5</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>-0.000152</v>
+        <v>-5.5e-05</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>-0.000589</v>
+        <v>-0.000226</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>3.3e-05</v>
+        <v>8.4e-05</v>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
@@ -7174,13 +7174,13 @@
         <v>0.5</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>-0.000248</v>
+        <v>-3.9e-05</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>-0.000606</v>
+        <v>-0.000206</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>0.000201</v>
+        <v>0.000234</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -7206,13 +7206,13 @@
         <v>0.5</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>-3.1e-05</v>
+        <v>-0.00012</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>-0.000229</v>
+        <v>-0.000276</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>0.000392</v>
+        <v>7.9e-05</v>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
@@ -7238,13 +7238,13 @@
         <v>0.9</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>-0.000276</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>-0.0009300000000000001</v>
+        <v>-0.000329</v>
       </c>
       <c r="G177" s="4" t="n">
-        <v>0.000487</v>
+        <v>0.000664</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -7270,13 +7270,13 @@
         <v>0.9</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>-0.000164</v>
+        <v>-8.7e-05</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>-0.00101</v>
+        <v>-0.000501</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>0.000245</v>
+        <v>0.000398</v>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
@@ -7302,13 +7302,13 @@
         <v>0.9</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>-0.00043</v>
+        <v>-0.000229</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>-0.001315</v>
+        <v>-0.001044</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>0.000106</v>
+        <v>0.000342</v>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
@@ -7334,13 +7334,13 @@
         <v>0.9</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>-0.000821</v>
+        <v>-6.1e-05</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>-0.0015</v>
+        <v>-0.000319</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>0.00026</v>
+        <v>0.000701</v>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
@@ -7366,13 +7366,13 @@
         <v>0.9</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>0.000398</v>
+        <v>6.499999999999999e-05</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>-0.000224</v>
+        <v>-0.000376</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>0.001238</v>
+        <v>0.000909</v>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
@@ -7819,19 +7819,19 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-3e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.002192</v>
+        <v>0.000445</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.041089</v>
+        <v>-0.003935</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>-1e-06</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.032109</v>
+        <v>0.004236</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>3611</v>
@@ -8039,19 +8039,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.061</v>
+        <v>-0.066</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.099</v>
+        <v>-0.013</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.095</v>
+        <v>-0.118</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.122</v>
+        <v>-0.152</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="3">
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.061</v>
+        <v>-0.066</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>1</v>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.099</v>
+        <v>-0.013</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>-0.164</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.095</v>
+        <v>-0.118</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>0.034</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.122</v>
+        <v>-0.152</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.195</v>
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-0.019</v>
+        <v>0.018</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.173</v>
@@ -8320,15 +8320,15 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8396,52 +8396,52 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>-0.000020*</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>[-0.000044, -0.000002]</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>-0.000020*</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>[-0.000036, -0.000005]</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>-0.000016*</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>[-0.000030, -0.000003]</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>-0.000012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>[-0.000027, 0.000000]</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
           <t>-0.000009</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>[-0.000027, 0.000010]</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>-0.000012</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>[-0.000026, 0.000006]</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>-0.000011</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>[-0.000024, 0.000005]</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>-0.000003</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>[-0.000016, 0.000010]</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>0.000007</t>
-        </is>
-      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>[-0.000016, 0.000039]</t>
+          <t>[-0.000032, 0.000008]</t>
         </is>
       </c>
     </row>
@@ -8453,52 +8453,52 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0.000727</t>
+          <t>0.000033</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000024, 0.001417]</t>
+          <t>[-0.000582, 0.000760]</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.000488</t>
+          <t>0.000313</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000013, 0.001046]</t>
+          <t>[-0.000187, 0.000760]</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>0.000352*</t>
+          <t>0.000206</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>[0.000005, 0.000764]</t>
+          <t>[-0.000160, 0.000620]</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>0.000509*</t>
+          <t>0.000298</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>[0.000148, 0.000923]</t>
+          <t>[-0.000110, 0.000695]</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>0.000520</t>
+          <t>0.000153</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>[-0.000005, 0.001501]</t>
+          <t>[-0.000478, 0.000640]</t>
         </is>
       </c>
     </row>
@@ -8510,52 +8510,52 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.000361</t>
+          <t>-0.000563</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000244, 0.001097]</t>
+          <t>[-0.001915, 0.000531]</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.000064</t>
+          <t>-0.000277</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000401, 0.000547]</t>
+          <t>[-0.000899, 0.000087]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>-0.000112</t>
+          <t>-0.000348</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000435, 0.000193]</t>
+          <t>[-0.000722, 0.000016]</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>-0.000047</t>
+          <t>-0.000526*</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>[-0.000717, 0.000295]</t>
+          <t>[-0.001143, -0.000030]</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-0.000064</t>
+          <t>-0.000931*</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>[-0.001096, 0.001167]</t>
+          <t>[-0.001850, -0.000257]</t>
         </is>
       </c>
     </row>
@@ -8567,52 +8567,52 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>0.000230</t>
+          <t>-0.002339</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[-0.002190, 0.001796]</t>
+          <t>[-0.004545, 0.000192]</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>-0.000758</t>
+          <t>-0.001350*</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[-0.001367, 0.000669]</t>
+          <t>[-0.002590, -0.000550]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>-0.000580</t>
+          <t>-0.001138*</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[-0.001296, 0.000209]</t>
+          <t>[-0.002023, -0.000458]</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>-0.000745</t>
+          <t>-0.001760*</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[-0.001758, 0.000646]</t>
+          <t>[-0.002694, -0.000695]</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-0.000598</t>
+          <t>-0.002560*</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[-0.002110, 0.002208]</t>
+          <t>[-0.003982, -0.000946]</t>
         </is>
       </c>
     </row>
@@ -8624,52 +8624,52 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>0.000055</t>
+          <t>0.001124</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>[-0.001013, 0.001057]</t>
+          <t>[-0.000411, 0.001996]</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.000303</t>
+          <t>0.000481</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000488, 0.000897]</t>
+          <t>[-0.000343, 0.001108]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>-0.000130</t>
+          <t>0.000162</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000523, 0.000373]</t>
+          <t>[-0.000348, 0.000610]</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>-0.000080</t>
+          <t>0.000187</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>[-0.000575, 0.000461]</t>
+          <t>[-0.000403, 0.000710]</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0.000098</t>
+          <t>0.000329</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>[-0.001180, 0.000714]</t>
+          <t>[-0.000354, 0.001088]</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0.0023</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -8723,7 +8723,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="4">
@@ -8731,7 +8731,7 @@
         <v>0.5</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="5">
@@ -8739,7 +8739,7 @@
         <v>0.75</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="6">
@@ -8747,7 +8747,7 @@
         <v>0.9</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.001</v>
+        <v>0.0134</v>
       </c>
     </row>
   </sheetData>
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>2e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.83</v>
+        <v>0.628</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.000267</v>
+        <v>-0.000129</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.388</v>
+        <v>0.742</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -8865,14 +8865,14 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.0005509999999999999</v>
+        <v>-3e-05</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.048</v>
+        <v>0.984</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.000599</v>
+        <v>-0.00098</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.432</v>
+        <v>0.406</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.4e-05</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.854</v>
+        <v>0.152</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -8937,10 +8937,10 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.6e-05</v>
+        <v>-1e-05</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1</v>
+        <v>0.324</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4e-05</v>
+        <v>-4e-05</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0.9</v>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.000476</v>
+        <v>0.000563</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.368</v>
+        <v>0.272</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.000393</v>
+        <v>0.000113</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.648</v>
+        <v>0.908</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.3e-05</v>
+        <v>0.0005330000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.962</v>
+        <v>0.328</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9057,14 +9057,14 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.8e-05</v>
+        <v>-6e-06</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.042</v>
+        <v>0.416</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9081,10 +9081,10 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.000228</v>
+        <v>8.899999999999999e-05</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.504</v>
+        <v>0.754</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-7.4e-05</v>
+        <v>0.000593</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.958</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.000207</v>
+        <v>0.001093</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.87</v>
+        <v>0.068</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.1e-05</v>
+        <v>-0.000241</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -9235,8 +9235,8 @@
       <c r="A2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="B2" s="5" t="n">
-        <v>0</v>
+      <c r="B2" s="4" t="n">
+        <v>0.10134</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -9264,8 +9264,8 @@
       <c r="A3" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>0</v>
+      <c r="B3" s="4" t="n">
+        <v>0.06666999999999999</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -9293,8 +9293,8 @@
       <c r="A4" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>0</v>
+      <c r="B4" s="4" t="n">
+        <v>0.06438000000000001</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -9322,8 +9322,8 @@
       <c r="A5" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>0</v>
+      <c r="B5" s="4" t="n">
+        <v>0.08822000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -9351,8 +9351,8 @@
       <c r="A6" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>0</v>
+      <c r="B6" s="4" t="n">
+        <v>0.13065</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -9741,17 +9741,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Negative effect in significant quantiles.</t>
         </is>
       </c>
     </row>
@@ -9768,17 +9768,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10, q0.50, q0.75, q0.90</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Negative effect in significant quantiles.</t>
         </is>
       </c>
     </row>
@@ -9795,17 +9795,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10, q0.25, q0.50, q0.75, q0.90</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Negative effect in significant quantiles.</t>
         </is>
       </c>
     </row>
@@ -9822,17 +9822,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10, q0.90</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Positive effect in significant quantiles.</t>
         </is>
       </c>
     </row>
